--- a/Test Case/Test_Case WebApp.xlsx
+++ b/Test Case/Test_Case WebApp.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JOB SEARCH\QA Project\Test Case\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68158738-6B6B-4712-8D21-212ABC6C4F38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC1FEF10-D139-4582-940F-4FDF06C12BA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Test Cases" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Test Cases'!$I$1:$I$78</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Test Cases'!$I$1:$I$87</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="647" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1003" uniqueCount="401">
   <si>
     <t>Project Name</t>
   </si>
@@ -442,9 +442,6 @@
     <t>Test Start Date</t>
   </si>
   <si>
-    <t>Book catrgory price drop down box</t>
-  </si>
-  <si>
     <t xml:space="preserve">1. Go to the homepage                 2.Go to books                                     3.Click price dropdown box  </t>
   </si>
   <si>
@@ -856,9 +853,6 @@
     <t>TC054</t>
   </si>
   <si>
-    <t>Computer-&gt;Desktops catrgory price drop down box</t>
-  </si>
-  <si>
     <t>Computer-&gt;Desktopscatrgory display per page drop down box</t>
   </si>
   <si>
@@ -941,6 +935,297 @@
   </si>
   <si>
     <t>Reopenned</t>
+  </si>
+  <si>
+    <t>Book catrgory price drop down box Low to High</t>
+  </si>
+  <si>
+    <t>Book catrgory price drop down box High to Low</t>
+  </si>
+  <si>
+    <t>Book catrgory name drop down box A to Z</t>
+  </si>
+  <si>
+    <t>Book catrgory name drop down box Z to A</t>
+  </si>
+  <si>
+    <t>Book catrgory created on dropbox</t>
+  </si>
+  <si>
+    <t>TC061</t>
+  </si>
+  <si>
+    <t>TC062</t>
+  </si>
+  <si>
+    <t>TC063</t>
+  </si>
+  <si>
+    <t>TC064</t>
+  </si>
+  <si>
+    <t>TC065</t>
+  </si>
+  <si>
+    <t>TC066</t>
+  </si>
+  <si>
+    <t>TC067</t>
+  </si>
+  <si>
+    <t>TC068</t>
+  </si>
+  <si>
+    <t>TC069</t>
+  </si>
+  <si>
+    <t>TC070</t>
+  </si>
+  <si>
+    <t>TC071</t>
+  </si>
+  <si>
+    <t>TC072</t>
+  </si>
+  <si>
+    <t>TC073</t>
+  </si>
+  <si>
+    <t>TC074</t>
+  </si>
+  <si>
+    <t>TC075</t>
+  </si>
+  <si>
+    <t>TC076</t>
+  </si>
+  <si>
+    <t>TC077</t>
+  </si>
+  <si>
+    <t>TC078</t>
+  </si>
+  <si>
+    <t>TC079</t>
+  </si>
+  <si>
+    <t>TC080</t>
+  </si>
+  <si>
+    <t>TC081</t>
+  </si>
+  <si>
+    <t>TC082</t>
+  </si>
+  <si>
+    <t>TC083</t>
+  </si>
+  <si>
+    <t>TC084</t>
+  </si>
+  <si>
+    <t>TC085</t>
+  </si>
+  <si>
+    <t>TC086</t>
+  </si>
+  <si>
+    <t>TC087</t>
+  </si>
+  <si>
+    <t>TC088</t>
+  </si>
+  <si>
+    <t>TC089</t>
+  </si>
+  <si>
+    <t>TC090</t>
+  </si>
+  <si>
+    <t>TC091</t>
+  </si>
+  <si>
+    <t>TC092</t>
+  </si>
+  <si>
+    <t>TC093</t>
+  </si>
+  <si>
+    <t>TC094</t>
+  </si>
+  <si>
+    <t>TC095</t>
+  </si>
+  <si>
+    <t>Computer-&gt;Desktops catrgory price Low to High drop down box</t>
+  </si>
+  <si>
+    <t>Computer-&gt;Desktops catrgory High to Low price drop down box</t>
+  </si>
+  <si>
+    <t>Computer-&gt;Desktops catrgory name A to Z drop down box</t>
+  </si>
+  <si>
+    <t>Computer-&gt;Desktops catrgory name Z to A drop down box</t>
+  </si>
+  <si>
+    <t>Computer-&gt;Desktops catrgorycreatedon drop down box</t>
+  </si>
+  <si>
+    <t>Computer-&gt;Desktops add to compare list</t>
+  </si>
+  <si>
+    <t>Computer-&gt;Desktops remove from compare list</t>
+  </si>
+  <si>
+    <t>Computer-&gt;Desktops list from compare</t>
+  </si>
+  <si>
+    <t>Computer-&gt;Desktops wishlist</t>
+  </si>
+  <si>
+    <t>All Computer-&gt;Desktops wishlist</t>
+  </si>
+  <si>
+    <t>All Computer-&gt;Desktops add to cart</t>
+  </si>
+  <si>
+    <t>All Computer-&gt;Desktops email a friend</t>
+  </si>
+  <si>
+    <t>All Computer-&gt;Desktops email a friend button</t>
+  </si>
+  <si>
+    <t>All Computer-&gt;Desktops quantity button</t>
+  </si>
+  <si>
+    <t>Check all Computer-&gt;Desktops quantity button work</t>
+  </si>
+  <si>
+    <t>Check all Computer-&gt;Desktops product tags link</t>
+  </si>
+  <si>
+    <t>Sorted by product tag 'computers'</t>
+  </si>
+  <si>
+    <t>1. Go to homepage                          2. Go to Computer-&gt;Desktops                                  3. Select every desktop and try to add on compare list</t>
+  </si>
+  <si>
+    <t>Desktops should add to compare list and redirect to compare page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All the Desktops added to compare list and redirected to compare page </t>
+  </si>
+  <si>
+    <t>1. Go to homepage                          2. Go to Computer-&gt;Desktops                                  3. Go to compare list                        4. Click remove Desktops</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desktops should remove from compare list </t>
+  </si>
+  <si>
+    <t xml:space="preserve">All the Desktops removed from compare list and redirected to compare page </t>
+  </si>
+  <si>
+    <t>1. Go to homepage                          2. Go to Computer-&gt;Desktops                                3. Go to compare list                        4. Click clear list</t>
+  </si>
+  <si>
+    <t>1. Go to homepage                          2. Go to Computer-&gt;Desktops                                  3. Select all the books individually                         4. Click  wishlist</t>
+  </si>
+  <si>
+    <t>Desktops should add to the wishlist</t>
+  </si>
+  <si>
+    <t>Desktops added to wish list</t>
+  </si>
+  <si>
+    <t>1. Go to homepage                          2. Go to Computer-&gt;Desktops                              3. Select all the Desktops individually                                     4. Check all the Desktops have wishlist</t>
+  </si>
+  <si>
+    <t>Desktops should have wishlist</t>
+  </si>
+  <si>
+    <t>All the Desktopsdoesnot have wishlist</t>
+  </si>
+  <si>
+    <t>Desktops should have add to cart</t>
+  </si>
+  <si>
+    <t>All the Desktops doesnot have add to cart</t>
+  </si>
+  <si>
+    <t>1. Go to homepage                          2. Go to Computer-&gt;Desktops                                 3. Select all the Desktops individually                                     4. Check all the Desktops have add to cart button</t>
+  </si>
+  <si>
+    <t>1. Go to homepage                          2. Go to Desktops                                 3. Select all the Desktops individually                                       4. Click email a friend</t>
+  </si>
+  <si>
+    <t>Desktops should redirect to email page</t>
+  </si>
+  <si>
+    <t>All the Desktops redirectt to email page</t>
+  </si>
+  <si>
+    <t>Assigned</t>
+  </si>
+  <si>
+    <t>1. Go to homepage                          2. Go to Computer-&gt;Desktops                           3. Select all the Desktops individually                                     4. Check all the Desktops have email friend button</t>
+  </si>
+  <si>
+    <t>1. Go to homepage                          2. Go to Computer-&gt;Desktops                                 3. Select all the Desktops individually                                     4. Check all the Desktops  have quantity button</t>
+  </si>
+  <si>
+    <t>Desktops should have quantity button</t>
+  </si>
+  <si>
+    <t>All the Desktops does have quantity button</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Go to homepage                          2. Go to Computer-&gt;Desktops                             3. Select all the Desktops individually                                     4. Click all the Desktops quantity button </t>
+  </si>
+  <si>
+    <t>Desktops quantity button should work</t>
+  </si>
+  <si>
+    <t>All the Desktops quantity button worked fine</t>
+  </si>
+  <si>
+    <t>1. Go to homepage                          2. Go to Computer-&gt;Desktops                                 3. Select all the books individually                         4. Click all the books product tags link</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Go to homepage                          2. Go to Computer-&gt;Desktops                                3. Click on product tag 'nice'                         </t>
+  </si>
+  <si>
+    <t>Desktops product tags should redirect to another page</t>
+  </si>
+  <si>
+    <t>All the Desktops product tags redirect to another page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Go to homepage                          2. Go to Computer-&gt;Desktops                               3. Click on product tag 'computers'                    </t>
+  </si>
+  <si>
+    <t>Computers should sorted by product tags</t>
+  </si>
+  <si>
+    <t>All the Computers are sorted by product tags</t>
+  </si>
+  <si>
+    <t>Check pages of 'book'</t>
+  </si>
+  <si>
+    <t>1. Go to homepage                          2. Go to books                                   3. Select all the books individually                         4. Click all the books product tags link                                                      5. Click the pages</t>
+  </si>
+  <si>
+    <t>Pages should change</t>
+  </si>
+  <si>
+    <t>Pages changed</t>
+  </si>
+  <si>
+    <t>Check pages of 'computer'</t>
+  </si>
+  <si>
+    <t>1. Go to homepage                          2. Go to Computer-&gt;Desktops                                 3. Select all the computers individually                                     4. Click all the computer product tags link                                                      5. Click the pages</t>
   </si>
 </sst>
 </file>
@@ -1135,56 +1420,7 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="62">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7030A0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="19">
     <dxf>
       <fill>
         <patternFill>
@@ -1202,7 +1438,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FF7030A0"/>
+          <bgColor rgb="FFFFFF00"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1258,13 +1494,6 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor rgb="FFFFFF00"/>
         </patternFill>
       </fill>
@@ -1272,252 +1501,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor rgb="FF7030A0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7030A0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7030A0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7030A0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1868,7 +1852,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L78"/>
+  <dimension ref="A1:L199"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="15" customWidth="1"/>
@@ -1964,7 +1948,7 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B7" s="1"/>
       <c r="C7" s="15">
@@ -2016,7 +2000,7 @@
       <c r="C10"/>
       <c r="F10"/>
       <c r="G10" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="H10" s="5"/>
     </row>
@@ -2026,7 +2010,7 @@
       <c r="C11"/>
       <c r="F11"/>
       <c r="G11" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="H11" s="4"/>
     </row>
@@ -2036,7 +2020,7 @@
       <c r="C12"/>
       <c r="F12"/>
       <c r="G12" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="H12" s="6"/>
     </row>
@@ -2046,7 +2030,7 @@
       <c r="C13"/>
       <c r="F13"/>
       <c r="G13" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="H13" s="18"/>
     </row>
@@ -2056,7 +2040,7 @@
       <c r="C14"/>
       <c r="F14"/>
       <c r="G14" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="H14" s="19"/>
     </row>
@@ -2112,7 +2096,7 @@
         <v>13</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="L18" s="2" t="s">
         <v>14</v>
@@ -2659,7 +2643,7 @@
         <v>31</v>
       </c>
       <c r="K34" s="9" t="s">
-        <v>301</v>
+        <v>380</v>
       </c>
       <c r="L34" s="13"/>
     </row>
@@ -2863,23 +2847,23 @@
     </row>
     <row r="41" spans="1:12" s="9" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A41" s="17" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B41" s="13" t="s">
+        <v>305</v>
+      </c>
+      <c r="C41" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="C41" s="13" t="s">
+      <c r="D41" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E41" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="D41" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E41" s="9" t="s">
+      <c r="F41" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="F41" s="13" t="s">
-        <v>142</v>
-      </c>
       <c r="G41" s="9" t="s">
         <v>20</v>
       </c>
@@ -2894,24 +2878,24 @@
       </c>
       <c r="L41" s="13"/>
     </row>
-    <row r="42" spans="1:12" s="9" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" s="9" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A42" s="17" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B42" s="13" t="s">
-        <v>144</v>
+        <v>304</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="D42" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E42" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="F42" s="13" t="s">
         <v>141</v>
-      </c>
-      <c r="F42" s="13" t="s">
-        <v>142</v>
       </c>
       <c r="G42" s="9" t="s">
         <v>20</v>
@@ -2929,22 +2913,22 @@
     </row>
     <row r="43" spans="1:12" s="9" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A43" s="17" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B43" s="13" t="s">
-        <v>147</v>
+        <v>306</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="D43" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E43" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="F43" s="13" t="s">
         <v>141</v>
-      </c>
-      <c r="F43" s="13" t="s">
-        <v>142</v>
       </c>
       <c r="G43" s="9" t="s">
         <v>20</v>
@@ -2962,223 +2946,223 @@
     </row>
     <row r="44" spans="1:12" s="9" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A44" s="17" t="s">
+        <v>153</v>
+      </c>
+      <c r="B44" s="13" t="s">
+        <v>307</v>
+      </c>
+      <c r="C44" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="D44" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E44" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="F44" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="G44" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="H44" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I44" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J44" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="L44" s="13"/>
+    </row>
+    <row r="45" spans="1:12" s="9" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A45" s="17" t="s">
+        <v>161</v>
+      </c>
+      <c r="B45" s="13" t="s">
+        <v>308</v>
+      </c>
+      <c r="C45" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="D45" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E45" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="F45" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="G45" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="H45" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I45" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J45" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="L45" s="13"/>
+    </row>
+    <row r="46" spans="1:12" s="9" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A46" s="17" t="s">
+        <v>162</v>
+      </c>
+      <c r="B46" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="C46" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="D46" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E46" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="F46" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="G46" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="H46" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I46" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J46" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="L46" s="13"/>
+    </row>
+    <row r="47" spans="1:12" s="9" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A47" s="17" t="s">
+        <v>169</v>
+      </c>
+      <c r="B47" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="C47" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="D47" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E47" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="F47" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="G47" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="H47" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I47" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J47" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="L47" s="13"/>
+    </row>
+    <row r="48" spans="1:12" s="9" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A48" s="17" t="s">
+        <v>170</v>
+      </c>
+      <c r="B48" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="C48" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="D48" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E48" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="F48" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="G48" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="H48" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I48" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J48" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="L48" s="13"/>
+    </row>
+    <row r="49" spans="1:12" s="9" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A49" s="17" t="s">
+        <v>176</v>
+      </c>
+      <c r="B49" s="13" t="s">
         <v>154</v>
       </c>
-      <c r="B44" s="13" t="s">
-        <v>149</v>
-      </c>
-      <c r="C44" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="D44" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E44" s="13" t="s">
-        <v>151</v>
-      </c>
-      <c r="F44" s="13" t="s">
-        <v>152</v>
-      </c>
-      <c r="G44" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="H44" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="I44" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J44" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="L44" s="13"/>
-    </row>
-    <row r="45" spans="1:12" s="9" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A45" s="17" t="s">
-        <v>162</v>
-      </c>
-      <c r="B45" s="13" t="s">
+      <c r="C49" s="13" t="s">
         <v>155</v>
       </c>
-      <c r="C45" s="13" t="s">
+      <c r="D49" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E49" s="13" t="s">
         <v>156</v>
       </c>
-      <c r="D45" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E45" s="13" t="s">
+      <c r="F49" s="13" t="s">
         <v>157</v>
       </c>
-      <c r="F45" s="13" t="s">
+      <c r="G49" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="H49" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I49" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="J49" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="K49" s="9" t="s">
+        <v>380</v>
+      </c>
+      <c r="L49" s="13"/>
+    </row>
+    <row r="50" spans="1:12" s="9" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A50" s="17" t="s">
+        <v>181</v>
+      </c>
+      <c r="B50" s="13" t="s">
         <v>158</v>
       </c>
-      <c r="G45" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="H45" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="I45" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="J45" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="K45" s="9" t="s">
-        <v>301</v>
-      </c>
-      <c r="L45" s="13"/>
-    </row>
-    <row r="46" spans="1:12" s="9" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A46" s="17" t="s">
+      <c r="C50" s="13" t="s">
+        <v>159</v>
+      </c>
+      <c r="D50" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E50" s="13" t="s">
         <v>163</v>
       </c>
-      <c r="B46" s="13" t="s">
-        <v>159</v>
-      </c>
-      <c r="C46" s="13" t="s">
+      <c r="F50" s="13" t="s">
         <v>160</v>
-      </c>
-      <c r="D46" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E46" s="13" t="s">
-        <v>164</v>
-      </c>
-      <c r="F46" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="G46" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="H46" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="I46" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J46" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="L46" s="13"/>
-    </row>
-    <row r="47" spans="1:12" s="9" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A47" s="17" t="s">
-        <v>170</v>
-      </c>
-      <c r="B47" s="13" t="s">
-        <v>165</v>
-      </c>
-      <c r="C47" s="13" t="s">
-        <v>166</v>
-      </c>
-      <c r="D47" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E47" s="13" t="s">
-        <v>167</v>
-      </c>
-      <c r="F47" s="13" t="s">
-        <v>168</v>
-      </c>
-      <c r="G47" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="H47" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="I47" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J47" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="L47" s="13"/>
-    </row>
-    <row r="48" spans="1:12" s="9" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A48" s="17" t="s">
-        <v>171</v>
-      </c>
-      <c r="B48" s="13" t="s">
-        <v>169</v>
-      </c>
-      <c r="C48" s="13" t="s">
-        <v>175</v>
-      </c>
-      <c r="D48" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E48" s="13" t="s">
-        <v>172</v>
-      </c>
-      <c r="F48" s="13" t="s">
-        <v>173</v>
-      </c>
-      <c r="G48" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="H48" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="I48" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J48" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="L48" s="13"/>
-    </row>
-    <row r="49" spans="1:12" s="9" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A49" s="17" t="s">
-        <v>177</v>
-      </c>
-      <c r="B49" s="13" t="s">
-        <v>174</v>
-      </c>
-      <c r="C49" s="13" t="s">
-        <v>176</v>
-      </c>
-      <c r="D49" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E49" s="13" t="s">
-        <v>172</v>
-      </c>
-      <c r="F49" s="13" t="s">
-        <v>173</v>
-      </c>
-      <c r="G49" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="H49" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="I49" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J49" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="L49" s="13"/>
-    </row>
-    <row r="50" spans="1:12" s="9" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A50" s="17" t="s">
-        <v>182</v>
-      </c>
-      <c r="B50" s="13" t="s">
-        <v>178</v>
-      </c>
-      <c r="C50" s="13" t="s">
-        <v>179</v>
-      </c>
-      <c r="D50" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E50" s="13" t="s">
-        <v>180</v>
-      </c>
-      <c r="F50" s="13" t="s">
-        <v>181</v>
       </c>
       <c r="G50" s="9" t="s">
         <v>20</v>
@@ -3196,94 +3180,88 @@
     </row>
     <row r="51" spans="1:12" s="9" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A51" s="17" t="s">
+        <v>186</v>
+      </c>
+      <c r="B51" s="13" t="s">
+        <v>164</v>
+      </c>
+      <c r="C51" s="13" t="s">
+        <v>165</v>
+      </c>
+      <c r="D51" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E51" s="13" t="s">
+        <v>166</v>
+      </c>
+      <c r="F51" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="G51" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="H51" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I51" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J51" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="L51" s="13"/>
+    </row>
+    <row r="52" spans="1:12" s="9" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A52" s="17" t="s">
         <v>187</v>
       </c>
-      <c r="B51" s="13" t="s">
-        <v>183</v>
-      </c>
-      <c r="C51" s="13" t="s">
-        <v>184</v>
-      </c>
-      <c r="D51" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E51" s="13" t="s">
-        <v>185</v>
-      </c>
-      <c r="F51" s="13" t="s">
-        <v>186</v>
-      </c>
-      <c r="G51" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="H51" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="I51" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="J51" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="K51" s="9" t="s">
-        <v>301</v>
-      </c>
-      <c r="L51" s="13"/>
-    </row>
-    <row r="52" spans="1:12" s="9" customFormat="1" ht="72" x14ac:dyDescent="0.3">
-      <c r="A52" s="17" t="s">
-        <v>188</v>
-      </c>
       <c r="B52" s="13" t="s">
-        <v>189</v>
+        <v>168</v>
       </c>
       <c r="C52" s="13" t="s">
-        <v>190</v>
+        <v>174</v>
       </c>
       <c r="D52" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E52" s="13" t="s">
-        <v>191</v>
+        <v>171</v>
       </c>
       <c r="F52" s="13" t="s">
-        <v>192</v>
+        <v>172</v>
       </c>
       <c r="G52" s="9" t="s">
         <v>20</v>
       </c>
       <c r="H52" s="9" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="I52" s="9" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="J52" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="K52" s="9" t="s">
-        <v>301</v>
+        <v>17</v>
       </c>
       <c r="L52" s="13"/>
     </row>
     <row r="53" spans="1:12" s="9" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A53" s="17" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B53" s="13" t="s">
-        <v>193</v>
+        <v>173</v>
       </c>
       <c r="C53" s="13" t="s">
-        <v>194</v>
+        <v>175</v>
       </c>
       <c r="D53" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E53" s="13" t="s">
-        <v>195</v>
+        <v>171</v>
       </c>
       <c r="F53" s="13" t="s">
-        <v>196</v>
+        <v>172</v>
       </c>
       <c r="G53" s="9" t="s">
         <v>20</v>
@@ -3299,24 +3277,24 @@
       </c>
       <c r="L53" s="13"/>
     </row>
-    <row r="54" spans="1:12" s="9" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:12" s="9" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A54" s="17" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B54" s="13" t="s">
-        <v>198</v>
+        <v>177</v>
       </c>
       <c r="C54" s="13" t="s">
-        <v>199</v>
+        <v>178</v>
       </c>
       <c r="D54" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E54" s="13" t="s">
-        <v>200</v>
+        <v>179</v>
       </c>
       <c r="F54" s="13" t="s">
-        <v>201</v>
+        <v>180</v>
       </c>
       <c r="G54" s="9" t="s">
         <v>20</v>
@@ -3332,125 +3310,131 @@
       </c>
       <c r="L54" s="13"/>
     </row>
-    <row r="55" spans="1:12" s="9" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:12" s="9" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A55" s="17" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B55" s="13" t="s">
-        <v>203</v>
+        <v>182</v>
       </c>
       <c r="C55" s="13" t="s">
-        <v>204</v>
+        <v>183</v>
       </c>
       <c r="D55" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E55" s="13" t="s">
-        <v>205</v>
+        <v>184</v>
       </c>
       <c r="F55" s="13" t="s">
-        <v>206</v>
+        <v>185</v>
       </c>
       <c r="G55" s="9" t="s">
         <v>20</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I55" s="9" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="J55" s="9" t="s">
-        <v>17</v>
+        <v>31</v>
+      </c>
+      <c r="K55" s="9" t="s">
+        <v>380</v>
       </c>
       <c r="L55" s="13"/>
     </row>
     <row r="56" spans="1:12" s="9" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A56" s="17" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B56" s="13" t="s">
-        <v>207</v>
+        <v>188</v>
       </c>
       <c r="C56" s="13" t="s">
-        <v>208</v>
+        <v>189</v>
       </c>
       <c r="D56" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E56" s="13" t="s">
-        <v>209</v>
+        <v>190</v>
       </c>
       <c r="F56" s="13" t="s">
-        <v>210</v>
+        <v>191</v>
       </c>
       <c r="G56" s="9" t="s">
         <v>20</v>
       </c>
       <c r="H56" s="9" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I56" s="9" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="J56" s="9" t="s">
-        <v>17</v>
+        <v>31</v>
+      </c>
+      <c r="K56" s="9" t="s">
+        <v>299</v>
       </c>
       <c r="L56" s="13"/>
     </row>
-    <row r="57" spans="1:12" s="9" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:12" s="9" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A57" s="17" t="s">
+        <v>228</v>
+      </c>
+      <c r="B57" s="13" t="s">
+        <v>192</v>
+      </c>
+      <c r="C57" s="13" t="s">
+        <v>193</v>
+      </c>
+      <c r="D57" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E57" s="13" t="s">
+        <v>194</v>
+      </c>
+      <c r="F57" s="13" t="s">
+        <v>195</v>
+      </c>
+      <c r="G57" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="H57" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I57" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J57" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="L57" s="13"/>
+    </row>
+    <row r="58" spans="1:12" s="9" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+      <c r="A58" s="17" t="s">
         <v>229</v>
       </c>
-      <c r="B57" s="13" t="s">
-        <v>214</v>
-      </c>
-      <c r="C57" s="13" t="s">
-        <v>215</v>
-      </c>
-      <c r="D57" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E57" s="13" t="s">
-        <v>216</v>
-      </c>
-      <c r="F57" s="13" t="s">
-        <v>217</v>
-      </c>
-      <c r="G57" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="H57" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="I57" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J57" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="L57" s="13"/>
-    </row>
-    <row r="58" spans="1:12" s="9" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A58" s="17" t="s">
-        <v>230</v>
-      </c>
       <c r="B58" s="13" t="s">
-        <v>220</v>
+        <v>197</v>
       </c>
       <c r="C58" s="13" t="s">
-        <v>221</v>
-      </c>
-      <c r="D58" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="D58" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E58" s="13" t="s">
-        <v>218</v>
+        <v>199</v>
       </c>
       <c r="F58" s="13" t="s">
-        <v>255</v>
-      </c>
-      <c r="G58" s="13" t="s">
+        <v>200</v>
+      </c>
+      <c r="G58" s="9" t="s">
         <v>20</v>
       </c>
       <c r="H58" s="9" t="s">
@@ -3466,223 +3450,220 @@
     </row>
     <row r="59" spans="1:12" s="9" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A59" s="17" t="s">
+        <v>230</v>
+      </c>
+      <c r="B59" s="13" t="s">
+        <v>202</v>
+      </c>
+      <c r="C59" s="13" t="s">
+        <v>203</v>
+      </c>
+      <c r="D59" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E59" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="F59" s="13" t="s">
+        <v>205</v>
+      </c>
+      <c r="G59" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="H59" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I59" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J59" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="L59" s="13"/>
+    </row>
+    <row r="60" spans="1:12" s="9" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+      <c r="A60" s="17" t="s">
         <v>231</v>
       </c>
-      <c r="B59" s="13" t="s">
-        <v>240</v>
-      </c>
-      <c r="C59" s="13" t="s">
-        <v>226</v>
-      </c>
-      <c r="D59" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E59" s="9" t="s">
+      <c r="B60" s="13" t="s">
+        <v>206</v>
+      </c>
+      <c r="C60" s="13" t="s">
+        <v>207</v>
+      </c>
+      <c r="D60" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E60" s="13" t="s">
+        <v>208</v>
+      </c>
+      <c r="F60" s="13" t="s">
+        <v>209</v>
+      </c>
+      <c r="G60" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="H60" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I60" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J60" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="L60" s="13"/>
+    </row>
+    <row r="61" spans="1:12" s="9" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+      <c r="A61" s="17" t="s">
+        <v>232</v>
+      </c>
+      <c r="B61" s="13" t="s">
+        <v>213</v>
+      </c>
+      <c r="C61" s="13" t="s">
+        <v>214</v>
+      </c>
+      <c r="D61" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E61" s="13" t="s">
+        <v>215</v>
+      </c>
+      <c r="F61" s="13" t="s">
+        <v>216</v>
+      </c>
+      <c r="G61" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="H61" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I61" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J61" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="L61" s="13"/>
+    </row>
+    <row r="62" spans="1:12" s="9" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A62" s="17" t="s">
+        <v>233</v>
+      </c>
+      <c r="B62" s="13" t="s">
+        <v>395</v>
+      </c>
+      <c r="C62" s="13" t="s">
+        <v>396</v>
+      </c>
+      <c r="D62" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E62" s="13" t="s">
+        <v>397</v>
+      </c>
+      <c r="F62" s="13" t="s">
+        <v>398</v>
+      </c>
+      <c r="G62" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="H62" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I62" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J62" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="L62" s="13"/>
+    </row>
+    <row r="63" spans="1:12" s="9" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A63" s="17" t="s">
+        <v>234</v>
+      </c>
+      <c r="B63" s="13" t="s">
+        <v>219</v>
+      </c>
+      <c r="C63" s="13" t="s">
+        <v>220</v>
+      </c>
+      <c r="D63" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="E63" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="F63" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="G63" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H63" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I63" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J63" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="L63" s="13"/>
+    </row>
+    <row r="64" spans="1:12" s="9" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+      <c r="A64" s="17" t="s">
+        <v>260</v>
+      </c>
+      <c r="B64" s="13" t="s">
+        <v>239</v>
+      </c>
+      <c r="C64" s="13" t="s">
+        <v>225</v>
+      </c>
+      <c r="D64" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E64" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="F64" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="F59" s="13" t="s">
-        <v>142</v>
-      </c>
-      <c r="G59" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="H59" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="I59" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J59" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="L59" s="13"/>
-    </row>
-    <row r="60" spans="1:12" s="9" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A60" s="17" t="s">
-        <v>232</v>
-      </c>
-      <c r="B60" s="13" t="s">
-        <v>222</v>
-      </c>
-      <c r="C60" s="13" t="s">
-        <v>239</v>
-      </c>
-      <c r="D60" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E60" s="9" t="s">
+      <c r="G64" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="H64" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I64" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J64" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="L64" s="13"/>
+    </row>
+    <row r="65" spans="1:12" s="9" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A65" s="17" t="s">
+        <v>261</v>
+      </c>
+      <c r="B65" s="13" t="s">
+        <v>221</v>
+      </c>
+      <c r="C65" s="13" t="s">
+        <v>238</v>
+      </c>
+      <c r="D65" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E65" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="F65" s="13" t="s">
         <v>141</v>
-      </c>
-      <c r="F60" s="13" t="s">
-        <v>142</v>
-      </c>
-      <c r="G60" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="H60" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="I60" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J60" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="L60" s="13"/>
-    </row>
-    <row r="61" spans="1:12" s="9" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A61" s="17" t="s">
-        <v>233</v>
-      </c>
-      <c r="B61" s="13" t="s">
-        <v>223</v>
-      </c>
-      <c r="C61" s="13" t="s">
-        <v>227</v>
-      </c>
-      <c r="D61" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E61" s="13" t="s">
-        <v>249</v>
-      </c>
-      <c r="F61" s="13" t="s">
-        <v>250</v>
-      </c>
-      <c r="G61" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="H61" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="I61" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J61" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="L61" s="13"/>
-    </row>
-    <row r="62" spans="1:12" s="9" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A62" s="17" t="s">
-        <v>234</v>
-      </c>
-      <c r="B62" s="13" t="s">
-        <v>224</v>
-      </c>
-      <c r="C62" s="13" t="s">
-        <v>228</v>
-      </c>
-      <c r="D62" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E62" s="13" t="s">
-        <v>251</v>
-      </c>
-      <c r="F62" s="13" t="s">
-        <v>252</v>
-      </c>
-      <c r="G62" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="H62" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="I62" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="J62" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="K62" s="9" t="s">
-        <v>301</v>
-      </c>
-      <c r="L62" s="13"/>
-    </row>
-    <row r="63" spans="1:12" s="9" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A63" s="17" t="s">
-        <v>235</v>
-      </c>
-      <c r="B63" s="13" t="s">
-        <v>225</v>
-      </c>
-      <c r="C63" s="13" t="s">
-        <v>253</v>
-      </c>
-      <c r="D63" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E63" s="13" t="s">
-        <v>254</v>
-      </c>
-      <c r="F63" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="G63" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="H63" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="I63" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J63" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="L63" s="13"/>
-    </row>
-    <row r="64" spans="1:12" s="9" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A64" s="17" t="s">
-        <v>261</v>
-      </c>
-      <c r="B64" s="13" t="s">
-        <v>236</v>
-      </c>
-      <c r="C64" s="13" t="s">
-        <v>241</v>
-      </c>
-      <c r="D64" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E64" s="13" t="s">
-        <v>218</v>
-      </c>
-      <c r="F64" s="13" t="s">
-        <v>255</v>
-      </c>
-      <c r="G64" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H64" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="I64" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J64" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="L64" s="13"/>
-    </row>
-    <row r="65" spans="1:12" s="9" customFormat="1" ht="72" x14ac:dyDescent="0.3">
-      <c r="A65" s="17" t="s">
-        <v>262</v>
-      </c>
-      <c r="B65" s="13" t="s">
-        <v>268</v>
-      </c>
-      <c r="C65" s="13" t="s">
-        <v>237</v>
-      </c>
-      <c r="D65" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E65" s="9" t="s">
-        <v>141</v>
-      </c>
-      <c r="F65" s="13" t="s">
-        <v>142</v>
       </c>
       <c r="G65" s="9" t="s">
         <v>20</v>
@@ -3700,22 +3681,22 @@
     </row>
     <row r="66" spans="1:12" s="9" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A66" s="17" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B66" s="13" t="s">
-        <v>238</v>
+        <v>222</v>
       </c>
       <c r="C66" s="13" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="D66" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="E66" s="9" t="s">
-        <v>141</v>
+      <c r="E66" s="13" t="s">
+        <v>248</v>
       </c>
       <c r="F66" s="13" t="s">
-        <v>142</v>
+        <v>249</v>
       </c>
       <c r="G66" s="9" t="s">
         <v>20</v>
@@ -3733,256 +3714,259 @@
     </row>
     <row r="67" spans="1:12" s="9" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A67" s="17" t="s">
+        <v>263</v>
+      </c>
+      <c r="B67" s="13" t="s">
+        <v>223</v>
+      </c>
+      <c r="C67" s="13" t="s">
+        <v>227</v>
+      </c>
+      <c r="D67" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E67" s="13" t="s">
+        <v>250</v>
+      </c>
+      <c r="F67" s="13" t="s">
+        <v>251</v>
+      </c>
+      <c r="G67" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="H67" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I67" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="J67" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="K67" s="9" t="s">
+        <v>380</v>
+      </c>
+      <c r="L67" s="13"/>
+    </row>
+    <row r="68" spans="1:12" s="9" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A68" s="17" t="s">
         <v>264</v>
       </c>
-      <c r="B67" s="13" t="s">
+      <c r="B68" s="13" t="s">
+        <v>224</v>
+      </c>
+      <c r="C68" s="13" t="s">
+        <v>252</v>
+      </c>
+      <c r="D68" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E68" s="13" t="s">
+        <v>253</v>
+      </c>
+      <c r="F68" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="G68" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="H68" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I68" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J68" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="L68" s="13"/>
+    </row>
+    <row r="69" spans="1:12" s="9" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A69" s="17" t="s">
+        <v>265</v>
+      </c>
+      <c r="B69" s="13" t="s">
+        <v>235</v>
+      </c>
+      <c r="C69" s="13" t="s">
+        <v>240</v>
+      </c>
+      <c r="D69" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E69" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="F69" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="G69" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H69" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I69" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J69" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="L69" s="13"/>
+    </row>
+    <row r="70" spans="1:12" s="9" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+      <c r="A70" s="17" t="s">
+        <v>266</v>
+      </c>
+      <c r="B70" s="13" t="s">
+        <v>267</v>
+      </c>
+      <c r="C70" s="13" t="s">
+        <v>236</v>
+      </c>
+      <c r="D70" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E70" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="F70" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="G70" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="H70" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I70" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J70" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="L70" s="13"/>
+    </row>
+    <row r="71" spans="1:12" s="9" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A71" s="17" t="s">
+        <v>268</v>
+      </c>
+      <c r="B71" s="13" t="s">
+        <v>237</v>
+      </c>
+      <c r="C71" s="13" t="s">
+        <v>241</v>
+      </c>
+      <c r="D71" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E71" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="F71" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="G71" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="H71" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I71" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J71" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="L71" s="13"/>
+    </row>
+    <row r="72" spans="1:12" s="9" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A72" s="17" t="s">
+        <v>275</v>
+      </c>
+      <c r="B72" s="13" t="s">
+        <v>243</v>
+      </c>
+      <c r="C72" s="13" t="s">
+        <v>242</v>
+      </c>
+      <c r="D72" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E72" s="13" t="s">
+        <v>248</v>
+      </c>
+      <c r="F72" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="G72" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="H72" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I72" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J72" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="L72" s="13"/>
+    </row>
+    <row r="73" spans="1:12" s="9" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+      <c r="A73" s="17" t="s">
+        <v>292</v>
+      </c>
+      <c r="B73" s="13" t="s">
         <v>244</v>
       </c>
-      <c r="C67" s="13" t="s">
-        <v>243</v>
-      </c>
-      <c r="D67" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E67" s="13" t="s">
-        <v>249</v>
-      </c>
-      <c r="F67" s="13" t="s">
-        <v>250</v>
-      </c>
-      <c r="G67" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="H67" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="I67" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J67" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="L67" s="13"/>
-    </row>
-    <row r="68" spans="1:12" s="9" customFormat="1" ht="72" x14ac:dyDescent="0.3">
-      <c r="A68" s="17" t="s">
-        <v>265</v>
-      </c>
-      <c r="B68" s="13" t="s">
+      <c r="C73" s="13" t="s">
         <v>245</v>
       </c>
-      <c r="C68" s="13" t="s">
+      <c r="D73" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E73" s="13" t="s">
+        <v>255</v>
+      </c>
+      <c r="F73" s="13" t="s">
+        <v>251</v>
+      </c>
+      <c r="G73" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="H73" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I73" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="J73" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="K73" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="L73" s="13"/>
+    </row>
+    <row r="74" spans="1:12" s="9" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A74" s="17" t="s">
+        <v>293</v>
+      </c>
+      <c r="B74" s="13" t="s">
         <v>246</v>
       </c>
-      <c r="D68" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E68" s="13" t="s">
+      <c r="C74" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="D74" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E74" s="13" t="s">
         <v>256</v>
       </c>
-      <c r="F68" s="13" t="s">
-        <v>252</v>
-      </c>
-      <c r="G68" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="H68" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="I68" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="J68" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="K68" s="9" t="s">
-        <v>301</v>
-      </c>
-      <c r="L68" s="13"/>
-    </row>
-    <row r="69" spans="1:12" s="9" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A69" s="17" t="s">
-        <v>266</v>
-      </c>
-      <c r="B69" s="13" t="s">
-        <v>247</v>
-      </c>
-      <c r="C69" s="13" t="s">
-        <v>248</v>
-      </c>
-      <c r="D69" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E69" s="13" t="s">
-        <v>257</v>
-      </c>
-      <c r="F69" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="G69" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="H69" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="I69" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J69" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="L69" s="13"/>
-    </row>
-    <row r="70" spans="1:12" s="9" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A70" s="17" t="s">
-        <v>267</v>
-      </c>
-      <c r="B70" s="13" t="s">
-        <v>270</v>
-      </c>
-      <c r="C70" s="13" t="s">
-        <v>271</v>
-      </c>
-      <c r="D70" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E70" s="13" t="s">
-        <v>272</v>
-      </c>
-      <c r="F70" s="13" t="s">
-        <v>273</v>
-      </c>
-      <c r="G70" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="H70" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="I70" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J70" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="L70" s="13"/>
-    </row>
-    <row r="71" spans="1:12" s="9" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A71" s="17" t="s">
-        <v>269</v>
-      </c>
-      <c r="B71" s="13" t="s">
-        <v>258</v>
-      </c>
-      <c r="C71" s="13" t="s">
-        <v>259</v>
-      </c>
-      <c r="D71" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E71" s="13" t="s">
-        <v>260</v>
-      </c>
-      <c r="F71" s="13" t="s">
-        <v>219</v>
-      </c>
-      <c r="G71" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H71" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="I71" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J71" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="L71" s="13"/>
-    </row>
-    <row r="72" spans="1:12" s="9" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A72" s="17" t="s">
-        <v>276</v>
-      </c>
-      <c r="B72" s="13" t="s">
-        <v>274</v>
-      </c>
-      <c r="C72" s="13" t="s">
-        <v>275</v>
-      </c>
-      <c r="D72" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E72" s="9" t="s">
-        <v>141</v>
-      </c>
-      <c r="F72" s="13" t="s">
-        <v>142</v>
-      </c>
-      <c r="G72" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="H72" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="I72" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J72" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="L72" s="13"/>
-    </row>
-    <row r="73" spans="1:12" s="9" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A73" s="17" t="s">
-        <v>294</v>
-      </c>
-      <c r="B73" s="13" t="s">
-        <v>277</v>
-      </c>
-      <c r="C73" s="13" t="s">
-        <v>283</v>
-      </c>
-      <c r="D73" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E73" s="9" t="s">
-        <v>141</v>
-      </c>
-      <c r="F73" s="13" t="s">
-        <v>142</v>
-      </c>
-      <c r="G73" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="H73" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="I73" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J73" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="L73" s="13"/>
-    </row>
-    <row r="74" spans="1:12" s="9" customFormat="1" ht="72" x14ac:dyDescent="0.3">
-      <c r="A74" s="17" t="s">
-        <v>295</v>
-      </c>
-      <c r="B74" s="13" t="s">
-        <v>278</v>
-      </c>
-      <c r="C74" s="13" t="s">
-        <v>284</v>
-      </c>
-      <c r="D74" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E74" s="9" t="s">
-        <v>141</v>
-      </c>
       <c r="F74" s="13" t="s">
-        <v>142</v>
+        <v>160</v>
       </c>
       <c r="G74" s="9" t="s">
         <v>20</v>
@@ -4000,22 +3984,22 @@
     </row>
     <row r="75" spans="1:12" s="9" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A75" s="17" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B75" s="13" t="s">
-        <v>280</v>
+        <v>269</v>
       </c>
       <c r="C75" s="13" t="s">
-        <v>285</v>
+        <v>270</v>
       </c>
       <c r="D75" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="E75" s="9" t="s">
-        <v>141</v>
+      <c r="E75" s="13" t="s">
+        <v>271</v>
       </c>
       <c r="F75" s="13" t="s">
-        <v>142</v>
+        <v>272</v>
       </c>
       <c r="G75" s="9" t="s">
         <v>20</v>
@@ -4033,103 +4017,1528 @@
     </row>
     <row r="76" spans="1:12" s="9" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A76" s="17" t="s">
+        <v>295</v>
+      </c>
+      <c r="B76" s="13" t="s">
+        <v>257</v>
+      </c>
+      <c r="C76" s="13" t="s">
+        <v>258</v>
+      </c>
+      <c r="D76" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E76" s="13" t="s">
+        <v>259</v>
+      </c>
+      <c r="F76" s="13" t="s">
+        <v>218</v>
+      </c>
+      <c r="G76" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H76" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I76" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J76" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="L76" s="13"/>
+    </row>
+    <row r="77" spans="1:12" s="9" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A77" s="17" t="s">
+        <v>296</v>
+      </c>
+      <c r="B77" s="13" t="s">
+        <v>273</v>
+      </c>
+      <c r="C77" s="13" t="s">
+        <v>274</v>
+      </c>
+      <c r="D77" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E77" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="F77" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="G77" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="H77" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I77" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J77" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="L77" s="13"/>
+    </row>
+    <row r="78" spans="1:12" s="9" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+      <c r="A78" s="17" t="s">
         <v>297</v>
       </c>
-      <c r="B76" s="13" t="s">
+      <c r="B78" s="13" t="s">
+        <v>344</v>
+      </c>
+      <c r="C78" s="13" t="s">
+        <v>281</v>
+      </c>
+      <c r="D78" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E78" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="F78" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="G78" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="H78" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I78" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J78" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="L78" s="13"/>
+    </row>
+    <row r="79" spans="1:12" s="9" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+      <c r="A79" s="17" t="s">
+        <v>309</v>
+      </c>
+      <c r="B79" s="13" t="s">
+        <v>345</v>
+      </c>
+      <c r="C79" s="13" t="s">
+        <v>281</v>
+      </c>
+      <c r="D79" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E79" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="F79" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="G79" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="H79" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I79" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J79" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="L79" s="13"/>
+    </row>
+    <row r="80" spans="1:12" s="9" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+      <c r="A80" s="17" t="s">
+        <v>310</v>
+      </c>
+      <c r="B80" s="13" t="s">
+        <v>346</v>
+      </c>
+      <c r="C80" s="13" t="s">
+        <v>281</v>
+      </c>
+      <c r="D80" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E80" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="F80" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="G80" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="H80" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I80" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J80" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="L80" s="13"/>
+    </row>
+    <row r="81" spans="1:12" s="9" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+      <c r="A81" s="17" t="s">
+        <v>311</v>
+      </c>
+      <c r="B81" s="13" t="s">
+        <v>347</v>
+      </c>
+      <c r="C81" s="13" t="s">
+        <v>281</v>
+      </c>
+      <c r="D81" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E81" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="F81" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="G81" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="H81" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I81" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J81" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="L81" s="13"/>
+    </row>
+    <row r="82" spans="1:12" s="9" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+      <c r="A82" s="17" t="s">
+        <v>312</v>
+      </c>
+      <c r="B82" s="13" t="s">
+        <v>348</v>
+      </c>
+      <c r="C82" s="13" t="s">
+        <v>281</v>
+      </c>
+      <c r="D82" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E82" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="F82" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="G82" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="H82" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I82" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J82" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="L82" s="13"/>
+    </row>
+    <row r="83" spans="1:12" s="9" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+      <c r="A83" s="17" t="s">
+        <v>313</v>
+      </c>
+      <c r="B83" s="13" t="s">
+        <v>276</v>
+      </c>
+      <c r="C83" s="13" t="s">
+        <v>282</v>
+      </c>
+      <c r="D83" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E83" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="F83" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="G83" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="H83" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I83" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J83" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="L83" s="13"/>
+    </row>
+    <row r="84" spans="1:12" s="9" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A84" s="17" t="s">
+        <v>314</v>
+      </c>
+      <c r="B84" s="13" t="s">
+        <v>278</v>
+      </c>
+      <c r="C84" s="13" t="s">
+        <v>283</v>
+      </c>
+      <c r="D84" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E84" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="F84" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="G84" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="H84" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I84" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J84" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="L84" s="13"/>
+    </row>
+    <row r="85" spans="1:12" s="9" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A85" s="17" t="s">
+        <v>315</v>
+      </c>
+      <c r="B85" s="13" t="s">
+        <v>277</v>
+      </c>
+      <c r="C85" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D85" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E85" s="13" t="s">
+        <v>287</v>
+      </c>
+      <c r="F85" s="13" t="s">
+        <v>291</v>
+      </c>
+      <c r="G85" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="H85" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I85" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J85" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="L85" s="13"/>
+    </row>
+    <row r="86" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A86" s="17" t="s">
+        <v>316</v>
+      </c>
+      <c r="B86" s="13" t="s">
         <v>279</v>
       </c>
-      <c r="C76" s="13" t="s">
+      <c r="C86" s="13" t="s">
+        <v>285</v>
+      </c>
+      <c r="D86" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E86" s="13" t="s">
+        <v>288</v>
+      </c>
+      <c r="F86" s="13" t="s">
+        <v>290</v>
+      </c>
+      <c r="G86" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="H86" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I86" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="J86" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="K86" s="20" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A87" s="17" t="s">
+        <v>317</v>
+      </c>
+      <c r="B87" s="13" t="s">
+        <v>280</v>
+      </c>
+      <c r="C87" s="13" t="s">
         <v>286</v>
       </c>
-      <c r="D76" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E76" s="13" t="s">
+      <c r="D87" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E87" s="13" t="s">
         <v>289</v>
       </c>
-      <c r="F76" s="13" t="s">
-        <v>293</v>
-      </c>
-      <c r="G76" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="H76" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="I76" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J76" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="L76" s="13"/>
-    </row>
-    <row r="77" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A77" s="17" t="s">
-        <v>298</v>
-      </c>
-      <c r="B77" s="13" t="s">
-        <v>281</v>
-      </c>
-      <c r="C77" s="13" t="s">
-        <v>287</v>
-      </c>
-      <c r="D77" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E77" s="13" t="s">
-        <v>290</v>
-      </c>
-      <c r="F77" s="13" t="s">
-        <v>292</v>
-      </c>
-      <c r="G77" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="H77" s="9" t="s">
+      <c r="F87" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="G87" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="H87" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I87" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J87" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A88" s="17" t="s">
+        <v>318</v>
+      </c>
+      <c r="B88" s="13" t="s">
+        <v>349</v>
+      </c>
+      <c r="C88" s="13" t="s">
+        <v>361</v>
+      </c>
+      <c r="D88" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E88" s="13" t="s">
+        <v>362</v>
+      </c>
+      <c r="F88" s="13" t="s">
+        <v>363</v>
+      </c>
+      <c r="G88" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="H88" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I88" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J88" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K88" s="9"/>
+    </row>
+    <row r="89" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A89" s="17" t="s">
+        <v>319</v>
+      </c>
+      <c r="B89" s="13" t="s">
+        <v>350</v>
+      </c>
+      <c r="C89" s="13" t="s">
+        <v>364</v>
+      </c>
+      <c r="D89" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E89" s="13" t="s">
+        <v>365</v>
+      </c>
+      <c r="F89" s="13" t="s">
+        <v>366</v>
+      </c>
+      <c r="G89" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="H89" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I89" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J89" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K89" s="9"/>
+    </row>
+    <row r="90" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A90" s="17" t="s">
+        <v>320</v>
+      </c>
+      <c r="B90" s="13" t="s">
+        <v>351</v>
+      </c>
+      <c r="C90" s="13" t="s">
+        <v>367</v>
+      </c>
+      <c r="D90" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E90" s="13" t="s">
+        <v>365</v>
+      </c>
+      <c r="F90" s="13" t="s">
+        <v>366</v>
+      </c>
+      <c r="G90" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="H90" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I90" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J90" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K90" s="9"/>
+    </row>
+    <row r="91" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A91" s="17" t="s">
+        <v>321</v>
+      </c>
+      <c r="B91" s="13" t="s">
+        <v>352</v>
+      </c>
+      <c r="C91" s="13" t="s">
+        <v>368</v>
+      </c>
+      <c r="D91" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E91" s="13" t="s">
+        <v>369</v>
+      </c>
+      <c r="F91" s="13" t="s">
+        <v>370</v>
+      </c>
+      <c r="G91" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="H91" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I91" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J91" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K91" s="9"/>
+    </row>
+    <row r="92" spans="1:12" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A92" s="17" t="s">
+        <v>322</v>
+      </c>
+      <c r="B92" s="13" t="s">
+        <v>353</v>
+      </c>
+      <c r="C92" s="13" t="s">
+        <v>371</v>
+      </c>
+      <c r="D92" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E92" s="13" t="s">
+        <v>372</v>
+      </c>
+      <c r="F92" s="13" t="s">
+        <v>373</v>
+      </c>
+      <c r="G92" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="H92" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="I77" s="9" t="s">
+      <c r="I92" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="J77" s="9" t="s">
+      <c r="J92" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="K77" s="20" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="78" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A78" s="17" t="s">
+      <c r="K92" s="9" t="s">
         <v>299</v>
       </c>
-      <c r="B78" s="13" t="s">
-        <v>282</v>
-      </c>
-      <c r="C78" s="13" t="s">
-        <v>288</v>
-      </c>
-      <c r="D78" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E78" s="13" t="s">
-        <v>291</v>
-      </c>
-      <c r="F78" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="G78" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="H78" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="I78" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J78" s="9" t="s">
-        <v>17</v>
-      </c>
+    </row>
+    <row r="93" spans="1:12" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A93" s="17" t="s">
+        <v>323</v>
+      </c>
+      <c r="B93" s="13" t="s">
+        <v>354</v>
+      </c>
+      <c r="C93" s="13" t="s">
+        <v>376</v>
+      </c>
+      <c r="D93" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E93" s="13" t="s">
+        <v>374</v>
+      </c>
+      <c r="F93" s="13" t="s">
+        <v>375</v>
+      </c>
+      <c r="G93" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="H93" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I93" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="J93" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="K93" s="9" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+      <c r="A94" s="17" t="s">
+        <v>324</v>
+      </c>
+      <c r="B94" s="13" t="s">
+        <v>355</v>
+      </c>
+      <c r="C94" s="13" t="s">
+        <v>377</v>
+      </c>
+      <c r="D94" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E94" s="13" t="s">
+        <v>378</v>
+      </c>
+      <c r="F94" s="13" t="s">
+        <v>379</v>
+      </c>
+      <c r="G94" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="H94" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I94" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J94" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K94" s="9"/>
+    </row>
+    <row r="95" spans="1:12" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A95" s="17" t="s">
+        <v>325</v>
+      </c>
+      <c r="B95" s="13" t="s">
+        <v>356</v>
+      </c>
+      <c r="C95" s="13" t="s">
+        <v>381</v>
+      </c>
+      <c r="D95" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E95" s="13" t="s">
+        <v>199</v>
+      </c>
+      <c r="F95" s="13" t="s">
+        <v>200</v>
+      </c>
+      <c r="G95" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="H95" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I95" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="J95" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="K95" s="9" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A96" s="17" t="s">
+        <v>326</v>
+      </c>
+      <c r="B96" s="13" t="s">
+        <v>357</v>
+      </c>
+      <c r="C96" s="13" t="s">
+        <v>382</v>
+      </c>
+      <c r="D96" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E96" s="13" t="s">
+        <v>383</v>
+      </c>
+      <c r="F96" s="13" t="s">
+        <v>384</v>
+      </c>
+      <c r="G96" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="H96" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I96" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="J96" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="K96" s="9" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A97" s="17" t="s">
+        <v>327</v>
+      </c>
+      <c r="B97" s="13" t="s">
+        <v>358</v>
+      </c>
+      <c r="C97" s="13" t="s">
+        <v>385</v>
+      </c>
+      <c r="D97" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E97" s="13" t="s">
+        <v>386</v>
+      </c>
+      <c r="F97" s="13" t="s">
+        <v>387</v>
+      </c>
+      <c r="G97" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="H97" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I97" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J97" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K97" s="9"/>
+    </row>
+    <row r="98" spans="1:11" ht="72" x14ac:dyDescent="0.3">
+      <c r="A98" s="17" t="s">
+        <v>328</v>
+      </c>
+      <c r="B98" s="13" t="s">
+        <v>359</v>
+      </c>
+      <c r="C98" s="13" t="s">
+        <v>388</v>
+      </c>
+      <c r="D98" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E98" s="13" t="s">
+        <v>390</v>
+      </c>
+      <c r="F98" s="13" t="s">
+        <v>391</v>
+      </c>
+      <c r="G98" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="H98" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I98" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J98" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K98" s="9"/>
+    </row>
+    <row r="99" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A99" s="17" t="s">
+        <v>329</v>
+      </c>
+      <c r="B99" s="13" t="s">
+        <v>219</v>
+      </c>
+      <c r="C99" s="13" t="s">
+        <v>389</v>
+      </c>
+      <c r="D99" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="E99" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="F99" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="G99" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H99" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I99" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J99" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K99" s="9"/>
+    </row>
+    <row r="100" spans="1:11" ht="72" x14ac:dyDescent="0.3">
+      <c r="A100" s="17" t="s">
+        <v>330</v>
+      </c>
+      <c r="B100" s="13" t="s">
+        <v>239</v>
+      </c>
+      <c r="C100" s="13" t="s">
+        <v>225</v>
+      </c>
+      <c r="D100" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E100" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="F100" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="G100" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="H100" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I100" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J100" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K100" s="9"/>
+    </row>
+    <row r="101" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A101" s="17" t="s">
+        <v>331</v>
+      </c>
+      <c r="B101" s="13" t="s">
+        <v>221</v>
+      </c>
+      <c r="C101" s="13" t="s">
+        <v>238</v>
+      </c>
+      <c r="D101" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E101" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="F101" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="G101" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="H101" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I101" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J101" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K101" s="9"/>
+    </row>
+    <row r="102" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A102" s="17" t="s">
+        <v>332</v>
+      </c>
+      <c r="B102" s="13" t="s">
+        <v>222</v>
+      </c>
+      <c r="C102" s="13" t="s">
+        <v>226</v>
+      </c>
+      <c r="D102" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E102" s="13" t="s">
+        <v>248</v>
+      </c>
+      <c r="F102" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="G102" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="H102" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I102" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J102" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K102" s="9"/>
+    </row>
+    <row r="103" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A103" s="17" t="s">
+        <v>333</v>
+      </c>
+      <c r="B103" s="13" t="s">
+        <v>223</v>
+      </c>
+      <c r="C103" s="13" t="s">
+        <v>227</v>
+      </c>
+      <c r="D103" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E103" s="13" t="s">
+        <v>250</v>
+      </c>
+      <c r="F103" s="13" t="s">
+        <v>251</v>
+      </c>
+      <c r="G103" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="H103" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I103" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="J103" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="K103" s="9" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A104" s="17" t="s">
+        <v>334</v>
+      </c>
+      <c r="B104" s="13" t="s">
+        <v>224</v>
+      </c>
+      <c r="C104" s="13" t="s">
+        <v>252</v>
+      </c>
+      <c r="D104" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E104" s="13" t="s">
+        <v>253</v>
+      </c>
+      <c r="F104" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="G104" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="H104" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I104" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J104" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K104" s="9"/>
+    </row>
+    <row r="105" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A105" s="17" t="s">
+        <v>335</v>
+      </c>
+      <c r="B105" s="13" t="s">
+        <v>235</v>
+      </c>
+      <c r="C105" s="13" t="s">
+        <v>240</v>
+      </c>
+      <c r="D105" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E105" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="F105" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="G105" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H105" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I105" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J105" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K105" s="9"/>
+    </row>
+    <row r="106" spans="1:11" ht="72" x14ac:dyDescent="0.3">
+      <c r="A106" s="17" t="s">
+        <v>336</v>
+      </c>
+      <c r="B106" s="13" t="s">
+        <v>267</v>
+      </c>
+      <c r="C106" s="13" t="s">
+        <v>236</v>
+      </c>
+      <c r="D106" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E106" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="F106" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="G106" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="H106" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I106" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J106" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K106" s="9"/>
+    </row>
+    <row r="107" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A107" s="17" t="s">
+        <v>337</v>
+      </c>
+      <c r="B107" s="13" t="s">
+        <v>237</v>
+      </c>
+      <c r="C107" s="13" t="s">
+        <v>241</v>
+      </c>
+      <c r="D107" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E107" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="F107" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="G107" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="H107" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I107" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J107" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K107" s="9"/>
+    </row>
+    <row r="108" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A108" s="17" t="s">
+        <v>338</v>
+      </c>
+      <c r="B108" s="13" t="s">
+        <v>243</v>
+      </c>
+      <c r="C108" s="13" t="s">
+        <v>242</v>
+      </c>
+      <c r="D108" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E108" s="13" t="s">
+        <v>248</v>
+      </c>
+      <c r="F108" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="G108" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="H108" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I108" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J108" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K108" s="9"/>
+    </row>
+    <row r="109" spans="1:11" ht="72" x14ac:dyDescent="0.3">
+      <c r="A109" s="17" t="s">
+        <v>339</v>
+      </c>
+      <c r="B109" s="13" t="s">
+        <v>244</v>
+      </c>
+      <c r="C109" s="13" t="s">
+        <v>245</v>
+      </c>
+      <c r="D109" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E109" s="13" t="s">
+        <v>255</v>
+      </c>
+      <c r="F109" s="13" t="s">
+        <v>251</v>
+      </c>
+      <c r="G109" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="H109" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I109" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="J109" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="K109" s="9" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A110" s="17" t="s">
+        <v>340</v>
+      </c>
+      <c r="B110" s="13" t="s">
+        <v>246</v>
+      </c>
+      <c r="C110" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="D110" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E110" s="13" t="s">
+        <v>256</v>
+      </c>
+      <c r="F110" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="G110" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="H110" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I110" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J110" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K110" s="9"/>
+    </row>
+    <row r="111" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A111" s="17" t="s">
+        <v>341</v>
+      </c>
+      <c r="B111" s="13" t="s">
+        <v>269</v>
+      </c>
+      <c r="C111" s="13" t="s">
+        <v>270</v>
+      </c>
+      <c r="D111" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E111" s="13" t="s">
+        <v>271</v>
+      </c>
+      <c r="F111" s="13" t="s">
+        <v>272</v>
+      </c>
+      <c r="G111" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="H111" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I111" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J111" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K111" s="9"/>
+    </row>
+    <row r="112" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A112" s="17" t="s">
+        <v>342</v>
+      </c>
+      <c r="B112" s="13" t="s">
+        <v>360</v>
+      </c>
+      <c r="C112" s="13" t="s">
+        <v>392</v>
+      </c>
+      <c r="D112" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E112" s="13" t="s">
+        <v>393</v>
+      </c>
+      <c r="F112" s="13" t="s">
+        <v>394</v>
+      </c>
+      <c r="G112" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H112" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I112" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J112" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K112" s="9"/>
+    </row>
+    <row r="113" spans="1:11" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A113" s="17" t="s">
+        <v>343</v>
+      </c>
+      <c r="B113" s="13" t="s">
+        <v>399</v>
+      </c>
+      <c r="C113" s="13" t="s">
+        <v>400</v>
+      </c>
+      <c r="D113" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E113" s="13" t="s">
+        <v>397</v>
+      </c>
+      <c r="F113" s="13" t="s">
+        <v>398</v>
+      </c>
+      <c r="G113" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="H113" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I113" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J113" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K113" s="9"/>
+    </row>
+    <row r="114" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A114" s="17"/>
+    </row>
+    <row r="115" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A115" s="17"/>
+    </row>
+    <row r="116" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A116" s="17"/>
+    </row>
+    <row r="117" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A117" s="17"/>
+    </row>
+    <row r="118" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A118" s="17"/>
+    </row>
+    <row r="119" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A119" s="17"/>
+    </row>
+    <row r="120" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A120" s="17"/>
+    </row>
+    <row r="121" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A121" s="17"/>
+    </row>
+    <row r="122" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A122" s="17"/>
+    </row>
+    <row r="123" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A123" s="17"/>
+    </row>
+    <row r="124" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A124" s="17"/>
+    </row>
+    <row r="125" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A125" s="17"/>
+    </row>
+    <row r="126" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A126" s="17"/>
+    </row>
+    <row r="127" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A127" s="17"/>
+    </row>
+    <row r="128" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A128" s="17"/>
+    </row>
+    <row r="129" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A129" s="17"/>
+    </row>
+    <row r="130" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A130" s="17"/>
+    </row>
+    <row r="131" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A131" s="17"/>
+    </row>
+    <row r="132" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A132" s="17"/>
+    </row>
+    <row r="133" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A133" s="17"/>
+    </row>
+    <row r="134" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A134" s="17"/>
+    </row>
+    <row r="135" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A135" s="17"/>
+    </row>
+    <row r="136" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A136" s="17"/>
+    </row>
+    <row r="137" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A137" s="17"/>
+    </row>
+    <row r="138" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A138" s="17"/>
+    </row>
+    <row r="139" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A139" s="17"/>
+    </row>
+    <row r="140" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A140" s="17"/>
+    </row>
+    <row r="141" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A141" s="17"/>
+    </row>
+    <row r="142" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A142" s="17"/>
+    </row>
+    <row r="143" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A143" s="17"/>
+    </row>
+    <row r="144" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A144" s="17"/>
+    </row>
+    <row r="145" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A145" s="17"/>
+    </row>
+    <row r="146" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A146" s="17"/>
+    </row>
+    <row r="147" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A147" s="17"/>
+    </row>
+    <row r="148" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A148" s="17"/>
+    </row>
+    <row r="149" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A149" s="17"/>
+    </row>
+    <row r="150" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A150" s="17"/>
+    </row>
+    <row r="151" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A151" s="17"/>
+    </row>
+    <row r="152" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A152" s="17"/>
+    </row>
+    <row r="153" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A153" s="17"/>
+    </row>
+    <row r="154" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A154" s="17"/>
+    </row>
+    <row r="155" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A155" s="17"/>
+    </row>
+    <row r="156" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A156" s="17"/>
+    </row>
+    <row r="157" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A157" s="17"/>
+    </row>
+    <row r="158" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A158" s="17"/>
+    </row>
+    <row r="159" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A159" s="17"/>
+    </row>
+    <row r="160" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A160" s="17"/>
+    </row>
+    <row r="161" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A161" s="17"/>
+    </row>
+    <row r="162" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A162" s="17"/>
+    </row>
+    <row r="163" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A163" s="17"/>
+    </row>
+    <row r="164" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A164" s="17"/>
+    </row>
+    <row r="165" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A165" s="17"/>
+    </row>
+    <row r="166" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A166" s="17"/>
+    </row>
+    <row r="167" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A167" s="17"/>
+    </row>
+    <row r="168" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A168" s="17"/>
+    </row>
+    <row r="169" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A169" s="17"/>
+    </row>
+    <row r="170" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A170" s="17"/>
+    </row>
+    <row r="171" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A171" s="17"/>
+    </row>
+    <row r="172" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A172" s="17"/>
+    </row>
+    <row r="173" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A173" s="17"/>
+    </row>
+    <row r="174" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A174" s="17"/>
+    </row>
+    <row r="175" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A175" s="17"/>
+    </row>
+    <row r="176" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A176" s="17"/>
+    </row>
+    <row r="177" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A177" s="17"/>
+    </row>
+    <row r="178" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A178" s="17"/>
+    </row>
+    <row r="179" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A179" s="17"/>
+    </row>
+    <row r="180" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A180" s="17"/>
+    </row>
+    <row r="181" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A181" s="17"/>
+    </row>
+    <row r="182" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A182" s="17"/>
+    </row>
+    <row r="183" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A183" s="17"/>
+    </row>
+    <row r="184" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A184" s="17"/>
+    </row>
+    <row r="185" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A185" s="17"/>
+    </row>
+    <row r="186" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A186" s="17"/>
+    </row>
+    <row r="187" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A187" s="17"/>
+    </row>
+    <row r="188" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A188" s="17"/>
+    </row>
+    <row r="189" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A189" s="17"/>
+    </row>
+    <row r="190" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A190" s="17"/>
+    </row>
+    <row r="191" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A191" s="17"/>
+    </row>
+    <row r="192" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A192" s="17"/>
+    </row>
+    <row r="193" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A193" s="17"/>
+    </row>
+    <row r="194" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A194" s="17"/>
+    </row>
+    <row r="195" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A195" s="17"/>
+    </row>
+    <row r="196" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A196" s="17"/>
+    </row>
+    <row r="197" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A197" s="17"/>
+    </row>
+    <row r="198" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A198" s="17"/>
+    </row>
+    <row r="199" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A199" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -4144,70 +5553,67 @@
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="H1:H15 H17:H1048576">
-    <cfRule type="containsText" dxfId="61" priority="28" operator="containsText" text="INCOMPLETE">
+    <cfRule type="containsText" dxfId="18" priority="31" operator="containsText" text="INCOMPLETE">
       <formula>NOT(ISERROR(SEARCH("INCOMPLETE",H1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="60" priority="29" operator="containsText" text="FAIL">
+    <cfRule type="containsText" dxfId="17" priority="32" operator="containsText" text="FAIL">
       <formula>NOT(ISERROR(SEARCH("FAIL",H1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="59" priority="30" operator="containsText" text="PASS">
+    <cfRule type="containsText" dxfId="16" priority="33" operator="containsText" text="PASS">
       <formula>NOT(ISERROR(SEARCH("PASS",H1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1:K1048576">
-    <cfRule type="containsText" dxfId="58" priority="13" operator="containsText" text="N/A">
+    <cfRule type="containsText" dxfId="15" priority="16" operator="containsText" text="N/A">
       <formula>NOT(ISERROR(SEARCH("N/A",I1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="57" priority="14" operator="containsText" text="LOW">
+    <cfRule type="containsText" dxfId="14" priority="17" operator="containsText" text="LOW">
       <formula>NOT(ISERROR(SEARCH("LOW",I1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="56" priority="15" operator="containsText" text="MEDIUM">
+    <cfRule type="containsText" dxfId="13" priority="18" operator="containsText" text="MEDIUM">
       <formula>NOT(ISERROR(SEARCH("MEDIUM",I1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="55" priority="16" operator="containsText" text="HIGH">
+    <cfRule type="containsText" dxfId="12" priority="19" operator="containsText" text="HIGH">
       <formula>NOT(ISERROR(SEARCH("HIGH",I1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K1:K1048576">
-    <cfRule type="containsText" dxfId="10" priority="10" operator="containsText" text="New">
-      <formula>NOT(ISERROR(SEARCH("New",K1)))</formula>
+  <conditionalFormatting sqref="K1:K112 K114:K1048576">
+    <cfRule type="containsText" dxfId="11" priority="4" operator="containsText" text="Reopened">
+      <formula>NOT(ISERROR(SEARCH("Reopened",K1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="11" priority="9" operator="containsText" text="Assaigned">
+    <cfRule type="containsText" dxfId="10" priority="5" operator="containsText" text="In Pogress">
+      <formula>NOT(ISERROR(SEARCH("In Pogress",K1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="9" priority="6" operator="containsText" text="Assigned">
+      <formula>NOT(ISERROR(SEARCH("Assigned",K1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="8" priority="7" operator="containsText" text="Assaigned">
       <formula>NOT(ISERROR(SEARCH("Assaigned",K1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="12" priority="8" operator="containsText" text="In Progress">
+    <cfRule type="containsText" dxfId="7" priority="9" operator="containsText" text="Reopenned">
+      <formula>NOT(ISERROR(SEARCH("Reopenned",K1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="6" priority="10" operator="containsText" text="Closed">
+      <formula>NOT(ISERROR(SEARCH("Closed",K1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="5" priority="11" operator="containsText" text="In Progress">
       <formula>NOT(ISERROR(SEARCH("In Progress",K1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="13" priority="7" operator="containsText" text="Closed">
-      <formula>NOT(ISERROR(SEARCH("Closed",K1)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="14" priority="6" operator="containsText" text="Reopenned">
-      <formula>NOT(ISERROR(SEARCH("Reopenned",K1)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="15" priority="5" operator="containsText" text="Assaigned">
+    <cfRule type="containsText" dxfId="4" priority="12" operator="containsText" text="Assaigned">
       <formula>NOT(ISERROR(SEARCH("Assaigned",K1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="16" priority="4" operator="containsText" text="Assaigned">
-      <formula>NOT(ISERROR(SEARCH("Assaigned",K1)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="17" priority="3" operator="containsText" text="Assigned">
-      <formula>NOT(ISERROR(SEARCH("Assigned",K1)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="18" priority="2" operator="containsText" text="In Pogress">
-      <formula>NOT(ISERROR(SEARCH("In Pogress",K1)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="9" priority="1" operator="containsText" text="Reopened">
-      <formula>NOT(ISERROR(SEARCH("Reopened",K1)))</formula>
+    <cfRule type="containsText" dxfId="3" priority="13" operator="containsText" text="New">
+      <formula>NOT(ISERROR(SEARCH("New",K1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I1:J1048576" xr:uid="{E3DE18A1-EBF7-4867-B665-77E2B8F36544}">
-      <formula1>"HIGH, MEDIUM, LOW, N/A"</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H1:H15 H17:H1048576" xr:uid="{7E71C0DE-649D-4FEF-9437-444F26600051}">
       <formula1>"PASS, FAIL, INCOMPLETE"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K1:K1048576" xr:uid="{F6B2E189-FDCE-4077-B3C0-2FCC45F6CDD6}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I1:J1048576 K113" xr:uid="{E3DE18A1-EBF7-4867-B665-77E2B8F36544}">
+      <formula1>"HIGH, MEDIUM, LOW, N/A"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K1:K112 K114:K1048576" xr:uid="{F6B2E189-FDCE-4077-B3C0-2FCC45F6CDD6}">
       <formula1>"New, Assigned, In Pogress, Closed, Reopened"</formula1>
     </dataValidation>
   </dataValidations>
